--- a/out/MLP-mamba2_repeat_2_000006.xlsx
+++ b/out/MLP-mamba2_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.958776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8815939771807735</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.481593977180774</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.481593977180774</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.481593977180774</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003248462797255488</v>
+        <v>-0.0003524812174077378</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4181024663142252</v>
+        <v>0.4536705733070571</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8815939771807735</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8369961836136819</v>
+        <v>0.9082001314514829</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09655704483390672</v>
+        <v>-0.104771279911376</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3212205752005929</v>
+        <v>0.3485468121782732</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3212205752005929</v>
+        <v>0.3485468121782732</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.958776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3208703568741775</v>
+        <v>0.3482301782934898</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.075946277958668</v>
+        <v>0.9727677722503904</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.474905698494128</v>
+        <v>2.295702730791818</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2058701968973885</v>
+        <v>0.1861281524097758</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.958776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.80912948065815</v>
+        <v>1.693771699171346</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3606013917385919</v>
+        <v>0.3260208934474284</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.358776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.324562859092679</v>
+        <v>2.159777007724848</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1974782063535193</v>
+        <v>0.1785411436083204</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.358607540410862</v>
+        <v>2.190556955734323</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08156137515587222</v>
+        <v>0.07374009245621835</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.32404498262504</v>
+        <v>2.159308830265046</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1016189647386628</v>
+        <v>0.09187333683198588</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.958776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.445734833101518</v>
+        <v>2.269328770073407</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06118774313481479</v>
+        <v>0.05531961626917718</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.466422396086811</v>
+        <v>2.28803252125492</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04651913377651124</v>
+        <v>0.04205777984033682</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.49824677423385</v>
+        <v>2.316805441692556</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02057473954017705</v>
+        <v>0.01860305986686742</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.492837680581245</v>
+        <v>2.311914889784855</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01632621076253335</v>
+        <v>0.01476002795478746</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.504908886703893</v>
+        <v>2.322828088840387</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008094793092581742</v>
+        <v>0.007316832730693872</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.50475932549996</v>
+        <v>2.322692391541647</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004704996007174227</v>
+        <v>0.004254069891601648</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.506070246300825</v>
+        <v>2.323877328572201</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002348543403214299</v>
+        <v>0.002124534945800824</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.506062315980411</v>
+        <v>2.323869677157438</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001159232505764589</v>
+        <v>0.001047121227431703</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.506027844603967</v>
+        <v>2.323838043765392</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006692058611363528</v>
+        <v>0.0006057904583562008</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.506209751107729</v>
+        <v>2.324001949995817</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002204289815111627</v>
+        <v>0.0001981092803714436</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.505979744200737</v>
+        <v>2.323794111395352</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001095353485108232</v>
+        <v>9.830639277446798e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.50597601155959</v>
+        <v>2.323790254503337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.615490325271265e-05</v>
+        <v>5.126251099249565e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.505981167846279</v>
+        <v>2.323794413692994</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>2.107198491659588e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.358776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.505974150394831</v>
+        <v>2.323787630511679</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8815939771807735</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.505976144344625</v>
+        <v>2.323789084793573</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.505968809950481</v>
+        <v>2.323782082502752</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.505965324730173</v>
+        <v>2.323778220427656</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.505960777417988</v>
+        <v>2.323773673115471</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.505960867362638</v>
+        <v>2.323773763060121</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.505960009429053</v>
+        <v>2.323772905126536</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.505960237750088</v>
+        <v>2.323773133447571</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.505959442085876</v>
+        <v>2.323772337783359</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.505959504355249</v>
+        <v>2.323772400052732</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.505959532030526</v>
+        <v>2.323772427728009</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.505959684244548</v>
+        <v>2.323772579942032</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.505959338303587</v>
+        <v>2.32377223400107</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.505959414410599</v>
+        <v>2.323772310108082</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.50595958046226</v>
+        <v>2.323772476159744</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.50595994024086</v>
+        <v>2.323772835938343</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.505959960997318</v>
+        <v>2.323772856694801</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.505960064779606</v>
+        <v>2.323772960477089</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.505960293100641</v>
+        <v>2.323773188798124</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.505960168561895</v>
+        <v>2.323773064259378</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.505960196237172</v>
+        <v>2.323773091934656</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.358776160273009</v>
+        <v>1.599521431067185</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.505960251587726</v>
+        <v>2.323773147285209</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.505960514502856</v>
+        <v>2.32377341020034</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.505960431477026</v>
+        <v>2.323773327174509</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.505960223912449</v>
+        <v>2.323773119609932</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.505960237750088</v>
+        <v>2.323773133447571</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.505960376126472</v>
+        <v>2.323773271823955</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.505960092454883</v>
+        <v>2.323772988152367</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.505959919484403</v>
+        <v>2.323772815181886</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.505959815702114</v>
+        <v>2.323772711399597</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.505959960997318</v>
+        <v>2.323772856694801</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.505960203155991</v>
+        <v>2.323773098853474</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.505960030185511</v>
+        <v>2.323772925882994</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.505959732676283</v>
+        <v>2.323772628373767</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.505959718838645</v>
+        <v>2.323772614536128</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.505959352141225</v>
+        <v>2.323772247838709</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.505959352141225</v>
+        <v>2.323772247838709</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8815939771807735</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.505959289871853</v>
+        <v>2.323772185569336</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.505959186089564</v>
+        <v>2.323772081787047</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.505959013119083</v>
+        <v>2.323771908816566</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.505959061550818</v>
+        <v>2.323771957248301</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.505958701772218</v>
+        <v>2.323771597469701</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.505958660259302</v>
+        <v>2.323771555956786</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.505958715609856</v>
+        <v>2.323771611307339</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.50595877096041</v>
+        <v>2.323771666657894</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.505958812473326</v>
+        <v>2.323771708170809</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.505958542639375</v>
+        <v>2.323771438336859</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.505958597989929</v>
+        <v>2.323771493687412</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.505958743285133</v>
+        <v>2.323771638982616</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.958776160273009</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.505958708691037</v>
+        <v>2.32377160438852</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.505958694853399</v>
+        <v>2.323771590550882</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.505958784798048</v>
+        <v>2.323771680495532</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.505959103063733</v>
+        <v>2.323771998761216</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.505958923174433</v>
+        <v>2.323771818871916</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.7318388020611866</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.505958964687348</v>
+        <v>2.323771860384832</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.505958777879229</v>
+        <v>2.323771673576712</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.505958847067421</v>
+        <v>2.323771742764905</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.505958646421664</v>
+        <v>2.323771542119147</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-1.331838802061187</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.505958687934579</v>
+        <v>2.323771583632062</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>2.199521431067184</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.505958715609856</v>
+        <v>2.323771611307339</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000006.xlsx
+++ b/out/MLP-mamba2_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.958776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0003248462797255488</v>
+        <v>-0.000174408455880708</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4181024663142252</v>
+        <v>0.2244772684834239</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8369961836136819</v>
+        <v>0.4493793559386549</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.09655704483390672</v>
+        <v>-0.05184102803368092</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3212205752005929</v>
+        <v>0.1724618319938621</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3212205752005929</v>
+        <v>0.1724618319938621</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3208703568741775</v>
+        <v>0.1722805373627478</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.075946277958668</v>
+        <v>0.5569761529802977</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.474905698494128</v>
+        <v>1.287342238209314</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2058701968973885</v>
+        <v>0.1065711731551403</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.80912948065815</v>
+        <v>0.9426953088342797</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.3606013917385919</v>
+        <v>0.1866695167876825</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.358776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.324562859092679</v>
+        <v>1.209515409624033</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1974782063535193</v>
+        <v>0.1022267821458616</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.358607540410862</v>
+        <v>1.22713903624475</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.08156137515587222</v>
+        <v>0.0422211497842463</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.32404498262504</v>
+        <v>1.209247305107702</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1016189647386628</v>
+        <v>0.05260441987629785</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.445734833101518</v>
+        <v>1.272241688150389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06118774313481479</v>
+        <v>0.0316746558029264</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.466422396086811</v>
+        <v>1.282950882563995</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.04651913377651124</v>
+        <v>0.02408125345258727</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.49824677423385</v>
+        <v>1.299425198698333</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02057473954017705</v>
+        <v>0.01064961400752841</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.492837680581245</v>
+        <v>1.296623521106519</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01632621076253335</v>
+        <v>0.008449453998026572</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.504908886703893</v>
+        <v>1.302869746308101</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.008094793092581742</v>
+        <v>0.004187480921299259</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.50475932549996</v>
+        <v>1.302789920928919</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.004704996007174227</v>
+        <v>0.002432910224837556</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.506070246300825</v>
+        <v>1.303466046087119</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002348543403214299</v>
+        <v>0.001213955112418778</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.506062315980411</v>
+        <v>1.303459528405718</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001159232505764589</v>
+        <v>0.0005958014659377757</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.506027844603967</v>
+        <v>1.303439285126</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0006692058611363528</v>
+        <v>0.0003454535416797874</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.506209751107729</v>
+        <v>1.303531198536899</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002204289815111627</v>
+        <v>0.0001110624459265392</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.505979744200737</v>
+        <v>1.303409816331886</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001095353485108232</v>
+        <v>5.339056982904712e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.50597601155959</v>
+        <v>1.303405476274037</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>5.615490325271265e-05</v>
+        <v>2.680054969141058e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.505981167846279</v>
+        <v>1.303405853853079</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.58123458105224e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.505974150394831</v>
+        <v>1.303399767533069</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.245520447377725e-05</v>
+        <v>3.727602236888622e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.505976144344625</v>
+        <v>1.303398534341916</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.732487839350877e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.505968809950481</v>
+        <v>1.303392199481369</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.505965324730173</v>
+        <v>1.303387956871215</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.505960777417988</v>
+        <v>1.30338818519225</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.505960867362638</v>
+        <v>1.3033882751369</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.505960009429053</v>
+        <v>1.303387417203315</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.505960237750088</v>
+        <v>1.30338764552435</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.505959442085876</v>
+        <v>1.303386849860138</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.505959504355249</v>
+        <v>1.303386912129511</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.505959532030526</v>
+        <v>1.303386939804788</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.505959684244548</v>
+        <v>1.303387092018811</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.505959338303587</v>
+        <v>1.303386746077849</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.505959414410599</v>
+        <v>1.303386822184861</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.50595958046226</v>
+        <v>1.303386988236522</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.50595994024086</v>
+        <v>1.303387348015122</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.505959960997318</v>
+        <v>1.30338736877158</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.505960064779606</v>
+        <v>1.303387472553868</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.505960293100641</v>
+        <v>1.303387700874903</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.505960168561895</v>
+        <v>1.303387576336157</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.505960196237172</v>
+        <v>1.303387604011434</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.505960251587726</v>
+        <v>1.303387659361988</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.505960514502856</v>
+        <v>1.303387922277119</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.505960431477026</v>
+        <v>1.303387839251288</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.505960223912449</v>
+        <v>1.303387631686711</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.505960237750088</v>
+        <v>1.30338764552435</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.505960376126472</v>
+        <v>1.303387783900734</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.505960092454883</v>
+        <v>1.303387500229145</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.505959919484403</v>
+        <v>1.303387327258665</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.505959815702114</v>
+        <v>1.303387223476376</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.505959960997318</v>
+        <v>1.30338736877158</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.505960203155991</v>
+        <v>1.303387610930253</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.505960030185511</v>
+        <v>1.303387437959773</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.505959732676283</v>
+        <v>1.303387140450545</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.505959718838645</v>
+        <v>1.303387126612907</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.505959352141225</v>
+        <v>1.303386759915487</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.505959352141225</v>
+        <v>1.303386759915487</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.505959289871853</v>
+        <v>1.303386697646115</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.505959186089564</v>
+        <v>1.303386593863826</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.505959013119083</v>
+        <v>1.303386420893345</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.505959061550818</v>
+        <v>1.30338646932508</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.505958701772218</v>
+        <v>1.30338610954648</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.505958660259302</v>
+        <v>1.303386068033564</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.505958715609856</v>
+        <v>1.303386123384118</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.50595877096041</v>
+        <v>1.303386178734672</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.505958812473326</v>
+        <v>1.303386220247588</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.505958542639375</v>
+        <v>1.303385950413637</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.505958597989929</v>
+        <v>1.303386005764191</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8815939771807735</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.505958743285133</v>
+        <v>1.303386151059395</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.505958708691037</v>
+        <v>1.303386116465299</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.505958694853399</v>
+        <v>1.303386102627661</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.505958784798048</v>
+        <v>1.30338619257231</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.505959103063733</v>
+        <v>1.303386510837995</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.505958923174433</v>
+        <v>1.303386330948695</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.505958964687348</v>
+        <v>1.30338637246161</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.505958777879229</v>
+        <v>1.303386185653491</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.505958847067421</v>
+        <v>1.303386254841683</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.505958646421664</v>
+        <v>1.303386054195926</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.505958687934579</v>
+        <v>1.303386095708841</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>0.123605319917338</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.505958715609856</v>
+        <v>1.303386123384118</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000006.xlsx
+++ b/out/MLP-mamba2_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.5605577230453491</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000013</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.5270627737045288</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.09000000000000008</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.546911895275116</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.6893180012702942</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.1906040608882904</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.6478483080863953</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.316665917634964</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.5001966953277588</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5564734935760498</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2015811651945114</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4666858017444611</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3819301426410675</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.6822514533996582</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.3012574315071106</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2958953678607941</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.2913056313991547</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5238125920295715</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.5577924251556396</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.6815937757492065</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3938555419445038</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2099812477827072</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.3833067715167999</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3217134177684784</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.7266538143157959</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.2578737139701843</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.9299137592315674</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.6541594266891479</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5103599429130554</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3045265376567841</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.6157311797142029</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3574285805225372</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3067978620529175</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.5066150426864624</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.7655031681060791</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.40868279337883</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.3973056375980377</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.7116604447364807</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3433474898338318</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4503119289875031</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4957377314567566</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.8527130484580994</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.9292576909065247</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.8896517157554626</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000174408455880708</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2244772684834239</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3424442112445831</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4493793559386549</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05184102803368092</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.02629777975380421</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1724618319938621</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.7552032470703125</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1724618319938621</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.8370791673660278</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1722805373627478</v>
+        <v>0.1487550174629798</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.5569761529802977</v>
+        <v>0.2220724527183046</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.1784495264291763</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.287342238209314</v>
+        <v>0.5933421210574857</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1065711731551403</v>
+        <v>0.04249106159216588</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.9028318524360657</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.9426953088342797</v>
+        <v>0.4559277202391059</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.1866695167876825</v>
+        <v>0.07442712414977931</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6487910151481628</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.209515409624033</v>
+        <v>0.5623117357381268</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1022267821458616</v>
+        <v>0.04075900163180279</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.3727987110614777</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.22713903624475</v>
+        <v>0.5693384631679523</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0422211497842463</v>
+        <v>0.01683406125898829</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.9080535769462585</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.209247305107702</v>
+        <v>0.5622048559150095</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05260441987629785</v>
+        <v>0.0209733053068108</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.9134016633033752</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.272241688150389</v>
+        <v>0.5873212124477022</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0316746558029264</v>
+        <v>0.01262836336797664</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.9047191143035889</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.282950882563995</v>
+        <v>0.5915902860940718</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.02408125345258727</v>
+        <v>0.009599664042752726</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.5958728790283203</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.299425198698333</v>
+        <v>0.5981569335121708</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01064961400752841</v>
+        <v>0.00424317769124753</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.8633877635002136</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.296623521106519</v>
+        <v>0.5970368500988474</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.008449453998026572</v>
+        <v>0.003364674982507011</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.7190616130828857</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.302869746308101</v>
+        <v>0.5995243225849434</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004187480921299259</v>
+        <v>0.001665988815887771</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9565094709396362</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.302789920928919</v>
+        <v>0.5994894788253274</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002432910224837556</v>
+        <v>0.0009666730490402668</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.7129882574081421</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.303466046087119</v>
+        <v>0.59975636174072</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001213955112418778</v>
+        <v>0.0004808365245201334</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.02366508916020393</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.303459528405718</v>
+        <v>0.5997507568414505</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0005958014659377757</v>
+        <v>0.000236470445640063</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.3822199106216431</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.303439285126</v>
+        <v>0.5997396442596696</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003454535416797874</v>
+        <v>0.0001351814166719149</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.1218215674161911</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.303531198536899</v>
+        <v>0.5997734096240291</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001110624459265392</v>
+        <v>4.187137239341006e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.1111629381775856</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.303409816331886</v>
+        <v>0.5997218561803243</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>5.339056982904712e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.2749105989933014</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.303405476274037</v>
+        <v>0.5997171185196988</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.680054969141058e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.1693335771560669</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.303405853853079</v>
+        <v>0.5997143102936427</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8890897631645203</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.303399767533069</v>
+        <v>0.5997088447279239</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>3.727602236888622e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2742712795734406</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.303398534341916</v>
+        <v>0.599705460109473</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.6701772809028625</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.303392199481369</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.7195952534675598</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.303387956871215</v>
+        <v>0.5997001732142569</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1084959208965302</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.30338818519225</v>
+        <v>0.5997004015352917</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.03110984526574612</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.650235870066816</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.3033882751369</v>
+        <v>0.5997004914799416</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2661971151828766</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.303387417203315</v>
+        <v>0.5996996335463568</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.06408517807722092</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.30338764552435</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3476352393627167</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.303386849860138</v>
+        <v>0.5996990662031798</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1346491575241089</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.303386912129511</v>
+        <v>0.5996991284725529</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.4009296894073486</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.303386939804788</v>
+        <v>0.5996991561478298</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.477677971124649</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.303387092018811</v>
+        <v>0.599699308361853</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1617159694433212</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.303386746077849</v>
+        <v>0.5996989624208913</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.6059104800224304</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.303386822184861</v>
+        <v>0.599699038527903</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.2228087335824966</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.303386988236522</v>
+        <v>0.5996992045795645</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.8952435255050659</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.303387348015122</v>
+        <v>0.5996995643581645</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5797989964485168</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.30338736877158</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.7629963755607605</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.303387472553868</v>
+        <v>0.5996996888969107</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.1929298937320709</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.303387700874903</v>
+        <v>0.5996999172179455</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.2129576057195663</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.303387576336157</v>
+        <v>0.5996997926791993</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.4035509824752808</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.303387604011434</v>
+        <v>0.5996998203544761</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8144532442092896</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.303387659361988</v>
+        <v>0.59969987570503</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.09930684417486191</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.303387922277119</v>
+        <v>0.5997001386201608</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2604786455631256</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.303387839251288</v>
+        <v>0.5997000555943299</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.4427015483379364</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.303387631686711</v>
+        <v>0.5996998480297532</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4369619190692902</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.30338764552435</v>
+        <v>0.5996998618673915</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.2026330530643463</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.303387783900734</v>
+        <v>0.5997000002437762</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.1192705929279327</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.303387500229145</v>
+        <v>0.5996997165721876</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.2094641327857971</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.303387327258665</v>
+        <v>0.5996995436017069</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7614833116531372</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.303387223476376</v>
+        <v>0.5996994398194183</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.6363344192504883</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.30338736877158</v>
+        <v>0.5996995851146223</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.3304998576641083</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.303387610930253</v>
+        <v>0.5996998272732955</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.06061211600899696</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.650235870066816</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.303387437959773</v>
+        <v>0.5996996543028145</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.3443373143672943</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.303387140450545</v>
+        <v>0.5996993567935875</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.05022791028022766</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.303387126612907</v>
+        <v>0.5996993429559491</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.3518808782100677</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.303386759915487</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.7116342782974243</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.303386759915487</v>
+        <v>0.5996989762585299</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.08665429055690765</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.303386697646115</v>
+        <v>0.5996989139891568</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1740707755088806</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.303386593863826</v>
+        <v>0.5996988102068682</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.303661435842514</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.303386420893345</v>
+        <v>0.5996986372363875</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.08127120137214661</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.30338646932508</v>
+        <v>0.599698685668122</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1326417773962021</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.30338610954648</v>
+        <v>0.599698325889522</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.5447579026222229</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.303386068033564</v>
+        <v>0.5996982843766065</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.5257995128631592</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.303386123384118</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3042086064815521</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.303386178734672</v>
+        <v>0.5996983950777143</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.1614739894866943</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.650235870066816</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.303386220247588</v>
+        <v>0.5996984365906296</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.25890251994133</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.303385950413637</v>
+        <v>0.5996981667566795</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.7088030576705933</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.303386005764191</v>
+        <v>0.5996982221072334</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.2771648466587067</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.303386151059395</v>
+        <v>0.5996983674024374</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.532558798789978</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.303386116465299</v>
+        <v>0.5996983328083412</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2796731889247894</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.303386102627661</v>
+        <v>0.5996983189707026</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.9616557955741882</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.30338619257231</v>
+        <v>0.5996984089153528</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.8385200500488281</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.303386510837995</v>
+        <v>0.5996987271810374</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.05178098380565643</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.303386330948695</v>
+        <v>0.5996985472917373</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.1079720556735992</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.30338637246161</v>
+        <v>0.5996985888046527</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4979874193668365</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.303386185653491</v>
+        <v>0.5996984019965333</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1063923090696335</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.303386254841683</v>
+        <v>0.5996984711847259</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3224100768566132</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.303386054195926</v>
+        <v>0.5996982705389681</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4461246728897095</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.303386095708841</v>
+        <v>0.5996983120518834</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.6103733777999878</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.123605319917338</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.303386123384118</v>
+        <v>0.5996983397271602</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_2_000006.xlsx
+++ b/out/MLP-mamba2_repeat_2_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.5605577230453491</v>
+        <v>0.5605576038360596</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.02000000000000013</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.5270627737045288</v>
+        <v>0.527062714099884</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.09000000000000008</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.546911895275116</v>
+        <v>0.5469118356704712</v>
       </c>
       <c r="JB4" t="n">
         <v>0.4399999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.5564734935760498</v>
+        <v>0.556473433971405</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.5799999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3819301426410675</v>
+        <v>0.3819301724433899</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.6822514533996582</v>
+        <v>0.682251513004303</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.3012574315071106</v>
+        <v>0.301257461309433</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.5238125920295715</v>
+        <v>0.5238126516342163</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3938555419445038</v>
+        <v>0.3938556313514709</v>
       </c>
       <c r="JB21" t="n">
         <v>0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2099812477827072</v>
+        <v>0.2099812030792236</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3217134177684784</v>
+        <v>0.321713387966156</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.2578737139701843</v>
+        <v>0.2578736841678619</v>
       </c>
       <c r="JB26" t="n">
         <v>0.4399999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5103599429130554</v>
+        <v>0.5103600025177002</v>
       </c>
       <c r="JB29" t="n">
         <v>0.7199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.3045265376567841</v>
+        <v>0.3045265078544617</v>
       </c>
       <c r="JB30" t="n">
         <v>0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3574285805225372</v>
+        <v>0.3574285507202148</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.7116604447364807</v>
+        <v>0.7116603851318359</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.4503119289875031</v>
+        <v>0.4503119885921478</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.02629777975380421</v>
+        <v>0.02629777789115906</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.4399999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.8370791673660278</v>
+        <v>0.8370792269706726</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.4399999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.1784495264291763</v>
+        <v>0.1784495562314987</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.1600000000000001</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.9028318524360657</v>
+        <v>0.9028319716453552</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.3</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.7190616130828857</v>
+        <v>0.719061553478241</v>
       </c>
       <c r="JB58" t="n">
         <v>0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.1111629381775856</v>
+        <v>0.1111629158258438</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.2749105989933014</v>
+        <v>0.2749105095863342</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1693335771560669</v>
+        <v>0.1693335622549057</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2742712795734406</v>
+        <v>0.2742713093757629</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.6701772809028625</v>
+        <v>0.670177161693573</v>
       </c>
       <c r="JB69" t="n">
         <v>0.4399999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1084959208965302</v>
+        <v>0.1084959805011749</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2661971151828766</v>
+        <v>0.2661970853805542</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.06408517807722092</v>
+        <v>0.06408513337373734</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3476352393627167</v>
+        <v>0.3476351499557495</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1346491575241089</v>
+        <v>0.1346491724252701</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.8599999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.4009296894073486</v>
+        <v>0.4009296596050262</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1617159694433212</v>
+        <v>0.16171595454216</v>
       </c>
       <c r="JB79" t="n">
         <v>0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.7629963755607605</v>
+        <v>0.76299649477005</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.8144532442092896</v>
+        <v>0.8144531846046448</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.4427015483379364</v>
+        <v>0.4427014887332916</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4369619190692902</v>
+        <v>0.436961829662323</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.1192705929279327</v>
+        <v>0.1192706227302551</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.2094641327857971</v>
+        <v>0.2094640880823135</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.7614833116531372</v>
+        <v>0.7614830732345581</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.3443373143672943</v>
+        <v>0.3443372547626495</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.3518808782100677</v>
+        <v>0.3518808484077454</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.7116342782974243</v>
+        <v>0.7116343379020691</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.5799999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.08665429055690765</v>
+        <v>0.08665427565574646</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3042086064815521</v>
+        <v>0.3042085766792297</v>
       </c>
       <c r="JB111" t="n">
         <v>0.16</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.1614739894866943</v>
+        <v>0.1614740043878555</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.25890251994133</v>
+        <v>0.2589024901390076</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2796731889247894</v>
+        <v>0.2796732187271118</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.8385200500488281</v>
+        <v>0.8385199308395386</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1600000000000001</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.05178098380565643</v>
+        <v>0.05178099498152733</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3224100768566132</v>
+        <v>0.3224100470542908</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.1600000000000001</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4461246728897095</v>
+        <v>0.4461247324943542</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5800000000000001</v>
